--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/CODERS scripts/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19E2286A-1D9B-4C55-8259-3715807E5FC6}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EA1E23B-CEE6-4503-B61E-F57C96A666B6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ON" sheetId="1" r:id="rId1"/>
@@ -34,28 +34,121 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Sets the maximum capacity of technologies by period.</t>
   </si>
   <si>
-    <t>E_WIND_ON-NEW-1</t>
-  </si>
-  <si>
     <t>tech</t>
   </si>
   <si>
     <t>max MW per period</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-1</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-2</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-3</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-4</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-5</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-6</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-7</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-8</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-9</t>
+  </si>
+  <si>
+    <t>E_SOL_PV-NEW-10</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-1</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-2</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-3</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-4</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-5</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-6</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-7</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-8</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-9</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-10</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-1</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-2</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-3</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-4</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-5</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-6</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-7</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-8</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-9</t>
+  </si>
+  <si>
+    <t>E_WND_ON-NEW-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -397,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D36A0F-FD90-42AA-87C7-33795DBA1E16}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -410,12 +503,12 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>2025</v>
@@ -438,10 +531,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C4">
         <v>1000</v>
@@ -459,7 +552,675 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>1000</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5">
+        <v>1000</v>
+      </c>
+      <c r="F5">
+        <v>1000</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>1000</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
+      <c r="E6">
+        <v>1000</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>1000</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>1000</v>
+      </c>
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7">
+        <v>1000</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>1000</v>
+      </c>
+      <c r="C8">
+        <v>1000</v>
+      </c>
+      <c r="D8">
+        <v>1000</v>
+      </c>
+      <c r="E8">
+        <v>1000</v>
+      </c>
+      <c r="F8">
+        <v>1000</v>
+      </c>
+      <c r="G8">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>1000</v>
+      </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>1000</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+      <c r="F9">
+        <v>1000</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <v>1000</v>
+      </c>
+      <c r="C10">
+        <v>1000</v>
+      </c>
+      <c r="D10">
+        <v>1000</v>
+      </c>
+      <c r="E10">
+        <v>1000</v>
+      </c>
+      <c r="F10">
+        <v>1000</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11">
+        <v>1000</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>1000</v>
+      </c>
+      <c r="E11">
+        <v>1000</v>
+      </c>
+      <c r="F11">
+        <v>1000</v>
+      </c>
+      <c r="G11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12">
+        <v>1000</v>
+      </c>
+      <c r="C12">
+        <v>1000</v>
+      </c>
+      <c r="D12">
+        <v>1000</v>
+      </c>
+      <c r="E12">
+        <v>1000</v>
+      </c>
+      <c r="F12">
+        <v>1000</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>1000</v>
+      </c>
+      <c r="C13">
+        <v>1000</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
+      </c>
+      <c r="F13">
+        <v>1000</v>
+      </c>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14">
+        <v>1000</v>
+      </c>
+      <c r="C14">
+        <v>1000</v>
+      </c>
+      <c r="D14">
+        <v>1000</v>
+      </c>
+      <c r="E14">
+        <v>1000</v>
+      </c>
+      <c r="F14">
+        <v>1000</v>
+      </c>
+      <c r="G14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>1000</v>
+      </c>
+      <c r="C15">
+        <v>1000</v>
+      </c>
+      <c r="D15">
+        <v>1000</v>
+      </c>
+      <c r="E15">
+        <v>1000</v>
+      </c>
+      <c r="F15">
+        <v>1000</v>
+      </c>
+      <c r="G15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>1000</v>
+      </c>
+      <c r="C16">
+        <v>1000</v>
+      </c>
+      <c r="D16">
+        <v>1000</v>
+      </c>
+      <c r="E16">
+        <v>1000</v>
+      </c>
+      <c r="F16">
+        <v>1000</v>
+      </c>
+      <c r="G16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <v>1000</v>
+      </c>
+      <c r="C17">
+        <v>1000</v>
+      </c>
+      <c r="D17">
+        <v>1000</v>
+      </c>
+      <c r="E17">
+        <v>1000</v>
+      </c>
+      <c r="F17">
+        <v>1000</v>
+      </c>
+      <c r="G17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>1000</v>
+      </c>
+      <c r="C18">
+        <v>1000</v>
+      </c>
+      <c r="D18">
+        <v>1000</v>
+      </c>
+      <c r="E18">
+        <v>1000</v>
+      </c>
+      <c r="F18">
+        <v>1000</v>
+      </c>
+      <c r="G18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>1000</v>
+      </c>
+      <c r="C19">
+        <v>1000</v>
+      </c>
+      <c r="D19">
+        <v>1000</v>
+      </c>
+      <c r="E19">
+        <v>1000</v>
+      </c>
+      <c r="F19">
+        <v>1000</v>
+      </c>
+      <c r="G19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20">
+        <v>1000</v>
+      </c>
+      <c r="C20">
+        <v>1000</v>
+      </c>
+      <c r="D20">
+        <v>1000</v>
+      </c>
+      <c r="E20">
+        <v>1000</v>
+      </c>
+      <c r="F20">
+        <v>1000</v>
+      </c>
+      <c r="G20">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>1000</v>
+      </c>
+      <c r="C21">
+        <v>1000</v>
+      </c>
+      <c r="D21">
+        <v>1000</v>
+      </c>
+      <c r="E21">
+        <v>1000</v>
+      </c>
+      <c r="F21">
+        <v>1000</v>
+      </c>
+      <c r="G21">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1000</v>
+      </c>
+      <c r="C22">
+        <v>1000</v>
+      </c>
+      <c r="D22">
+        <v>1000</v>
+      </c>
+      <c r="E22">
+        <v>1000</v>
+      </c>
+      <c r="F22">
+        <v>1000</v>
+      </c>
+      <c r="G22">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23">
+        <v>1000</v>
+      </c>
+      <c r="C23">
+        <v>1000</v>
+      </c>
+      <c r="D23">
+        <v>1000</v>
+      </c>
+      <c r="E23">
+        <v>1000</v>
+      </c>
+      <c r="F23">
+        <v>1000</v>
+      </c>
+      <c r="G23">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24">
+        <v>1000</v>
+      </c>
+      <c r="C24">
+        <v>1000</v>
+      </c>
+      <c r="D24">
+        <v>1000</v>
+      </c>
+      <c r="E24">
+        <v>1000</v>
+      </c>
+      <c r="F24">
+        <v>1000</v>
+      </c>
+      <c r="G24">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25">
+        <v>1000</v>
+      </c>
+      <c r="C25">
+        <v>1000</v>
+      </c>
+      <c r="D25">
+        <v>1000</v>
+      </c>
+      <c r="E25">
+        <v>1000</v>
+      </c>
+      <c r="F25">
+        <v>1000</v>
+      </c>
+      <c r="G25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>1000</v>
+      </c>
+      <c r="C26">
+        <v>1000</v>
+      </c>
+      <c r="D26">
+        <v>1000</v>
+      </c>
+      <c r="E26">
+        <v>1000</v>
+      </c>
+      <c r="F26">
+        <v>1000</v>
+      </c>
+      <c r="G26">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27">
+        <v>1000</v>
+      </c>
+      <c r="C27">
+        <v>1000</v>
+      </c>
+      <c r="D27">
+        <v>1000</v>
+      </c>
+      <c r="E27">
+        <v>1000</v>
+      </c>
+      <c r="F27">
+        <v>1000</v>
+      </c>
+      <c r="G27">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>1000</v>
+      </c>
+      <c r="C28">
+        <v>1000</v>
+      </c>
+      <c r="D28">
+        <v>1000</v>
+      </c>
+      <c r="E28">
+        <v>1000</v>
+      </c>
+      <c r="F28">
+        <v>1000</v>
+      </c>
+      <c r="G28">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>1000</v>
+      </c>
+      <c r="C29">
+        <v>1000</v>
+      </c>
+      <c r="D29">
+        <v>1000</v>
+      </c>
+      <c r="E29">
+        <v>1000</v>
+      </c>
+      <c r="F29">
+        <v>1000</v>
+      </c>
+      <c r="G29">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30">
+        <v>1000</v>
+      </c>
+      <c r="C30">
+        <v>1000</v>
+      </c>
+      <c r="D30">
+        <v>1000</v>
+      </c>
+      <c r="E30">
+        <v>1000</v>
+      </c>
+      <c r="F30">
+        <v>1000</v>
+      </c>
+      <c r="G30">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31">
+        <v>1000</v>
+      </c>
+      <c r="C31">
+        <v>1000</v>
+      </c>
+      <c r="D31">
+        <v>1000</v>
+      </c>
+      <c r="E31">
+        <v>1000</v>
+      </c>
+      <c r="F31">
+        <v>1000</v>
+      </c>
+      <c r="G31">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32">
+        <v>1000</v>
+      </c>
+      <c r="C32">
+        <v>1000</v>
+      </c>
+      <c r="D32">
+        <v>1000</v>
+      </c>
+      <c r="E32">
+        <v>1000</v>
+      </c>
+      <c r="F32">
+        <v>1000</v>
+      </c>
+      <c r="G32">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33">
+        <v>1000</v>
+      </c>
+      <c r="C33">
+        <v>1000</v>
+      </c>
+      <c r="D33">
+        <v>1000</v>
+      </c>
+      <c r="E33">
+        <v>1000</v>
+      </c>
+      <c r="F33">
+        <v>1000</v>
+      </c>
+      <c r="G33">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/CODERS scripts/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EA1E23B-CEE6-4503-B61E-F57C96A666B6}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EEA40E0-8CDA-4D2C-80A6-ED3A7F45499A}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ON" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Sets the maximum capacity of technologies by period.</t>
   </si>
@@ -75,36 +75,6 @@
     <t>E_SOL_PV-NEW-10</t>
   </si>
   <si>
-    <t>E_HYD_ROR-NEW-1</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-2</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-3</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-4</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-5</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-6</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-7</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-8</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-9</t>
-  </si>
-  <si>
-    <t>E_HYD_ROR-NEW-10</t>
-  </si>
-  <si>
     <t>E_WND_ON-NEW-1</t>
   </si>
   <si>
@@ -133,6 +103,12 @@
   </si>
   <si>
     <t>E_WND_ON-NEW-10</t>
+  </si>
+  <si>
+    <t>E_BIO_G-NEW</t>
+  </si>
+  <si>
+    <t>E_HYD_DLY-NEW</t>
   </si>
 </sst>
 </file>
@@ -490,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D36A0F-FD90-42AA-87C7-33795DBA1E16}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -531,7 +507,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>1000</v>
@@ -554,7 +530,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>1000</v>
@@ -577,7 +553,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>1000</v>
@@ -600,7 +576,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>1000</v>
@@ -623,7 +599,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>1000</v>
@@ -646,7 +622,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>1000</v>
@@ -669,7 +645,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>1000</v>
@@ -692,7 +668,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>1000</v>
@@ -715,7 +691,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>1000</v>
@@ -738,7 +714,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>1000</v>
@@ -991,232 +967,48 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="C24">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="D24">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="E24">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="F24">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="G24">
-        <v>1000</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="C25">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="D25">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="E25">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="F25">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="G25">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26">
-        <v>1000</v>
-      </c>
-      <c r="C26">
-        <v>1000</v>
-      </c>
-      <c r="D26">
-        <v>1000</v>
-      </c>
-      <c r="E26">
-        <v>1000</v>
-      </c>
-      <c r="F26">
-        <v>1000</v>
-      </c>
-      <c r="G26">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27">
-        <v>1000</v>
-      </c>
-      <c r="C27">
-        <v>1000</v>
-      </c>
-      <c r="D27">
-        <v>1000</v>
-      </c>
-      <c r="E27">
-        <v>1000</v>
-      </c>
-      <c r="F27">
-        <v>1000</v>
-      </c>
-      <c r="G27">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28">
-        <v>1000</v>
-      </c>
-      <c r="C28">
-        <v>1000</v>
-      </c>
-      <c r="D28">
-        <v>1000</v>
-      </c>
-      <c r="E28">
-        <v>1000</v>
-      </c>
-      <c r="F28">
-        <v>1000</v>
-      </c>
-      <c r="G28">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29">
-        <v>1000</v>
-      </c>
-      <c r="C29">
-        <v>1000</v>
-      </c>
-      <c r="D29">
-        <v>1000</v>
-      </c>
-      <c r="E29">
-        <v>1000</v>
-      </c>
-      <c r="F29">
-        <v>1000</v>
-      </c>
-      <c r="G29">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30">
-        <v>1000</v>
-      </c>
-      <c r="C30">
-        <v>1000</v>
-      </c>
-      <c r="D30">
-        <v>1000</v>
-      </c>
-      <c r="E30">
-        <v>1000</v>
-      </c>
-      <c r="F30">
-        <v>1000</v>
-      </c>
-      <c r="G30">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31">
-        <v>1000</v>
-      </c>
-      <c r="C31">
-        <v>1000</v>
-      </c>
-      <c r="D31">
-        <v>1000</v>
-      </c>
-      <c r="E31">
-        <v>1000</v>
-      </c>
-      <c r="F31">
-        <v>1000</v>
-      </c>
-      <c r="G31">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32">
-        <v>1000</v>
-      </c>
-      <c r="C32">
-        <v>1000</v>
-      </c>
-      <c r="D32">
-        <v>1000</v>
-      </c>
-      <c r="E32">
-        <v>1000</v>
-      </c>
-      <c r="F32">
-        <v>1000</v>
-      </c>
-      <c r="G32">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33">
-        <v>1000</v>
-      </c>
-      <c r="C33">
-        <v>1000</v>
-      </c>
-      <c r="D33">
-        <v>1000</v>
-      </c>
-      <c r="E33">
-        <v>1000</v>
-      </c>
-      <c r="F33">
-        <v>1000</v>
-      </c>
-      <c r="G33">
-        <v>1000</v>
+        <v>4000</v>
       </c>
     </row>
   </sheetData>

--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/CODERS scripts/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EEA40E0-8CDA-4D2C-80A6-ED3A7F45499A}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{379357EB-1451-4751-B68C-EC4509A7C402}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="2595" yWindow="885" windowWidth="21600" windowHeight="11385" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ON" sheetId="1" r:id="rId1"/>
@@ -740,22 +740,22 @@
         <v>3</v>
       </c>
       <c r="B14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -763,22 +763,22 @@
         <v>4</v>
       </c>
       <c r="B15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -786,22 +786,22 @@
         <v>5</v>
       </c>
       <c r="B16">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C16">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D16">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E16">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F16">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -809,22 +809,22 @@
         <v>6</v>
       </c>
       <c r="B17">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C17">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D17">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E17">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F17">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -832,22 +832,22 @@
         <v>7</v>
       </c>
       <c r="B18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -855,22 +855,22 @@
         <v>8</v>
       </c>
       <c r="B19">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C19">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D19">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E19">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F19">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -878,22 +878,22 @@
         <v>9</v>
       </c>
       <c r="B20">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C20">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D20">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E20">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F20">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G20">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,22 +901,22 @@
         <v>10</v>
       </c>
       <c r="B21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -924,22 +924,22 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C22">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D22">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E22">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F22">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G22">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -947,22 +947,22 @@
         <v>12</v>
       </c>
       <c r="B23">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C23">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D23">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E23">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F23">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G23">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">

--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/CODERS scripts/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E06A2C56-302A-46DC-968A-FCD764C654B4}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBF05A67-2B30-4929-8C0C-148082002F09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="-13035" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ON" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>Sets the maximum capacity of technologies by period.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
   <si>
     <t>tech</t>
   </si>
@@ -114,10 +111,25 @@
     <t>reference</t>
   </si>
   <si>
-    <t>biogas potential</t>
-  </si>
-  <si>
-    <t>hydro potential</t>
+    <t>note</t>
+  </si>
+  <si>
+    <t>batches of new capacity</t>
+  </si>
+  <si>
+    <t>new biogas generation potential for ontario</t>
+  </si>
+  <si>
+    <t>new hydroelectric generation potential for ontario</t>
+  </si>
+  <si>
+    <t>Sets the maximum capacity of technologies by period. One sheet per region.</t>
+  </si>
+  <si>
+    <t>dq_est</t>
+  </si>
+  <si>
+    <t>asdas</t>
   </si>
 </sst>
 </file>
@@ -476,25 +488,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D36A0F-FD90-42AA-87C7-33795DBA1E16}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
       </c>
       <c r="B3">
         <v>2025</v>
@@ -517,471 +529,556 @@
       <c r="H3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>1000</v>
+      </c>
+      <c r="C4">
+        <v>1000</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4">
+        <v>1000</v>
+      </c>
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
-        <v>1000</v>
-      </c>
-      <c r="C4">
-        <v>1000</v>
-      </c>
-      <c r="D4">
-        <v>1000</v>
-      </c>
-      <c r="E4">
-        <v>1000</v>
-      </c>
-      <c r="F4">
-        <v>1000</v>
-      </c>
-      <c r="G4">
-        <v>1000</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5">
+        <v>1000</v>
+      </c>
+      <c r="C5">
+        <v>1000</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
+      <c r="E5">
+        <v>1000</v>
+      </c>
+      <c r="F5">
+        <v>1000</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
-        <v>1000</v>
-      </c>
-      <c r="C5">
-        <v>1000</v>
-      </c>
-      <c r="D5">
-        <v>1000</v>
-      </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
-      <c r="F5">
-        <v>1000</v>
-      </c>
-      <c r="G5">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6">
+        <v>1000</v>
+      </c>
+      <c r="C6">
+        <v>1000</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
+      <c r="E6">
+        <v>1000</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B6">
-        <v>1000</v>
-      </c>
-      <c r="C6">
-        <v>1000</v>
-      </c>
-      <c r="D6">
-        <v>1000</v>
-      </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
-      <c r="F6">
-        <v>1000</v>
-      </c>
-      <c r="G6">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7">
+        <v>1000</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>1000</v>
+      </c>
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7">
+        <v>1000</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B7">
-        <v>1000</v>
-      </c>
-      <c r="C7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>1000</v>
-      </c>
-      <c r="E7">
-        <v>1000</v>
-      </c>
-      <c r="F7">
-        <v>1000</v>
-      </c>
-      <c r="G7">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8">
+        <v>1000</v>
+      </c>
+      <c r="C8">
+        <v>1000</v>
+      </c>
+      <c r="D8">
+        <v>1000</v>
+      </c>
+      <c r="E8">
+        <v>1000</v>
+      </c>
+      <c r="F8">
+        <v>1000</v>
+      </c>
+      <c r="G8">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B8">
-        <v>1000</v>
-      </c>
-      <c r="C8">
-        <v>1000</v>
-      </c>
-      <c r="D8">
-        <v>1000</v>
-      </c>
-      <c r="E8">
-        <v>1000</v>
-      </c>
-      <c r="F8">
-        <v>1000</v>
-      </c>
-      <c r="G8">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9">
+        <v>1000</v>
+      </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>1000</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+      <c r="F9">
+        <v>1000</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B9">
-        <v>1000</v>
-      </c>
-      <c r="C9">
-        <v>1000</v>
-      </c>
-      <c r="D9">
-        <v>1000</v>
-      </c>
-      <c r="E9">
-        <v>1000</v>
-      </c>
-      <c r="F9">
-        <v>1000</v>
-      </c>
-      <c r="G9">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10">
+        <v>1000</v>
+      </c>
+      <c r="C10">
+        <v>1000</v>
+      </c>
+      <c r="D10">
+        <v>1000</v>
+      </c>
+      <c r="E10">
+        <v>1000</v>
+      </c>
+      <c r="F10">
+        <v>1000</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B10">
-        <v>1000</v>
-      </c>
-      <c r="C10">
-        <v>1000</v>
-      </c>
-      <c r="D10">
-        <v>1000</v>
-      </c>
-      <c r="E10">
-        <v>1000</v>
-      </c>
-      <c r="F10">
-        <v>1000</v>
-      </c>
-      <c r="G10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11">
+        <v>1000</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>1000</v>
+      </c>
+      <c r="E11">
+        <v>1000</v>
+      </c>
+      <c r="F11">
+        <v>1000</v>
+      </c>
+      <c r="G11">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B11">
-        <v>1000</v>
-      </c>
-      <c r="C11">
-        <v>1000</v>
-      </c>
-      <c r="D11">
-        <v>1000</v>
-      </c>
-      <c r="E11">
-        <v>1000</v>
-      </c>
-      <c r="F11">
-        <v>1000</v>
-      </c>
-      <c r="G11">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12">
+        <v>1000</v>
+      </c>
+      <c r="C12">
+        <v>1000</v>
+      </c>
+      <c r="D12">
+        <v>1000</v>
+      </c>
+      <c r="E12">
+        <v>1000</v>
+      </c>
+      <c r="F12">
+        <v>1000</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B12">
-        <v>1000</v>
-      </c>
-      <c r="C12">
-        <v>1000</v>
-      </c>
-      <c r="D12">
-        <v>1000</v>
-      </c>
-      <c r="E12">
-        <v>1000</v>
-      </c>
-      <c r="F12">
-        <v>1000</v>
-      </c>
-      <c r="G12">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13">
+        <v>1000</v>
+      </c>
+      <c r="C13">
+        <v>1000</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
+      </c>
+      <c r="F13">
+        <v>1000</v>
+      </c>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>2000</v>
+      </c>
+      <c r="C14">
+        <v>2000</v>
+      </c>
+      <c r="D14">
+        <v>2000</v>
+      </c>
+      <c r="E14">
+        <v>2000</v>
+      </c>
+      <c r="F14">
+        <v>2000</v>
+      </c>
+      <c r="G14">
+        <v>2000</v>
+      </c>
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>2000</v>
+      </c>
+      <c r="C15">
+        <v>2000</v>
+      </c>
+      <c r="D15">
+        <v>2000</v>
+      </c>
+      <c r="E15">
+        <v>2000</v>
+      </c>
+      <c r="F15">
+        <v>2000</v>
+      </c>
+      <c r="G15">
+        <v>2000</v>
+      </c>
+      <c r="H15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>2000</v>
+      </c>
+      <c r="C16">
+        <v>2000</v>
+      </c>
+      <c r="D16">
+        <v>2000</v>
+      </c>
+      <c r="E16">
+        <v>2000</v>
+      </c>
+      <c r="F16">
+        <v>2000</v>
+      </c>
+      <c r="G16">
+        <v>2000</v>
+      </c>
+      <c r="H16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>2000</v>
+      </c>
+      <c r="C17">
+        <v>2000</v>
+      </c>
+      <c r="D17">
+        <v>2000</v>
+      </c>
+      <c r="E17">
+        <v>2000</v>
+      </c>
+      <c r="F17">
+        <v>2000</v>
+      </c>
+      <c r="G17">
+        <v>2000</v>
+      </c>
+      <c r="H17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>2000</v>
+      </c>
+      <c r="C18">
+        <v>2000</v>
+      </c>
+      <c r="D18">
+        <v>2000</v>
+      </c>
+      <c r="E18">
+        <v>2000</v>
+      </c>
+      <c r="F18">
+        <v>2000</v>
+      </c>
+      <c r="G18">
+        <v>2000</v>
+      </c>
+      <c r="H18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19">
+        <v>2000</v>
+      </c>
+      <c r="C19">
+        <v>2000</v>
+      </c>
+      <c r="D19">
+        <v>2000</v>
+      </c>
+      <c r="E19">
+        <v>2000</v>
+      </c>
+      <c r="F19">
+        <v>2000</v>
+      </c>
+      <c r="G19">
+        <v>2000</v>
+      </c>
+      <c r="H19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20">
+        <v>2000</v>
+      </c>
+      <c r="C20">
+        <v>2000</v>
+      </c>
+      <c r="D20">
+        <v>2000</v>
+      </c>
+      <c r="E20">
+        <v>2000</v>
+      </c>
+      <c r="F20">
+        <v>2000</v>
+      </c>
+      <c r="G20">
+        <v>2000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21">
+        <v>2000</v>
+      </c>
+      <c r="C21">
+        <v>2000</v>
+      </c>
+      <c r="D21">
+        <v>2000</v>
+      </c>
+      <c r="E21">
+        <v>2000</v>
+      </c>
+      <c r="F21">
+        <v>2000</v>
+      </c>
+      <c r="G21">
+        <v>2000</v>
+      </c>
+      <c r="H21" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22">
+        <v>2000</v>
+      </c>
+      <c r="C22">
+        <v>2000</v>
+      </c>
+      <c r="D22">
+        <v>2000</v>
+      </c>
+      <c r="E22">
+        <v>2000</v>
+      </c>
+      <c r="F22">
+        <v>2000</v>
+      </c>
+      <c r="G22">
+        <v>2000</v>
+      </c>
+      <c r="H22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2000</v>
+      </c>
+      <c r="C23">
+        <v>2000</v>
+      </c>
+      <c r="D23">
+        <v>2000</v>
+      </c>
+      <c r="E23">
+        <v>2000</v>
+      </c>
+      <c r="F23">
+        <v>2000</v>
+      </c>
+      <c r="G23">
+        <v>2000</v>
+      </c>
+      <c r="H23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>22</v>
-      </c>
-      <c r="B13">
-        <v>1000</v>
-      </c>
-      <c r="C13">
-        <v>1000</v>
-      </c>
-      <c r="D13">
-        <v>1000</v>
-      </c>
-      <c r="E13">
-        <v>1000</v>
-      </c>
-      <c r="F13">
-        <v>1000</v>
-      </c>
-      <c r="G13">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14">
-        <v>2000</v>
-      </c>
-      <c r="C14">
-        <v>2000</v>
-      </c>
-      <c r="D14">
-        <v>2000</v>
-      </c>
-      <c r="E14">
-        <v>2000</v>
-      </c>
-      <c r="F14">
-        <v>2000</v>
-      </c>
-      <c r="G14">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15">
-        <v>2000</v>
-      </c>
-      <c r="C15">
-        <v>2000</v>
-      </c>
-      <c r="D15">
-        <v>2000</v>
-      </c>
-      <c r="E15">
-        <v>2000</v>
-      </c>
-      <c r="F15">
-        <v>2000</v>
-      </c>
-      <c r="G15">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>2000</v>
-      </c>
-      <c r="C16">
-        <v>2000</v>
-      </c>
-      <c r="D16">
-        <v>2000</v>
-      </c>
-      <c r="E16">
-        <v>2000</v>
-      </c>
-      <c r="F16">
-        <v>2000</v>
-      </c>
-      <c r="G16">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17">
-        <v>2000</v>
-      </c>
-      <c r="C17">
-        <v>2000</v>
-      </c>
-      <c r="D17">
-        <v>2000</v>
-      </c>
-      <c r="E17">
-        <v>2000</v>
-      </c>
-      <c r="F17">
-        <v>2000</v>
-      </c>
-      <c r="G17">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18">
-        <v>2000</v>
-      </c>
-      <c r="C18">
-        <v>2000</v>
-      </c>
-      <c r="D18">
-        <v>2000</v>
-      </c>
-      <c r="E18">
-        <v>2000</v>
-      </c>
-      <c r="F18">
-        <v>2000</v>
-      </c>
-      <c r="G18">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19">
-        <v>2000</v>
-      </c>
-      <c r="C19">
-        <v>2000</v>
-      </c>
-      <c r="D19">
-        <v>2000</v>
-      </c>
-      <c r="E19">
-        <v>2000</v>
-      </c>
-      <c r="F19">
-        <v>2000</v>
-      </c>
-      <c r="G19">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20">
-        <v>2000</v>
-      </c>
-      <c r="C20">
-        <v>2000</v>
-      </c>
-      <c r="D20">
-        <v>2000</v>
-      </c>
-      <c r="E20">
-        <v>2000</v>
-      </c>
-      <c r="F20">
-        <v>2000</v>
-      </c>
-      <c r="G20">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21">
-        <v>2000</v>
-      </c>
-      <c r="C21">
-        <v>2000</v>
-      </c>
-      <c r="D21">
-        <v>2000</v>
-      </c>
-      <c r="E21">
-        <v>2000</v>
-      </c>
-      <c r="F21">
-        <v>2000</v>
-      </c>
-      <c r="G21">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22">
-        <v>2000</v>
-      </c>
-      <c r="C22">
-        <v>2000</v>
-      </c>
-      <c r="D22">
-        <v>2000</v>
-      </c>
-      <c r="E22">
-        <v>2000</v>
-      </c>
-      <c r="F22">
-        <v>2000</v>
-      </c>
-      <c r="G22">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23">
-        <v>2000</v>
-      </c>
-      <c r="C23">
-        <v>2000</v>
-      </c>
-      <c r="D23">
-        <v>2000</v>
-      </c>
-      <c r="E23">
-        <v>2000</v>
-      </c>
-      <c r="F23">
-        <v>2000</v>
-      </c>
-      <c r="G23">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
       </c>
       <c r="B24">
         <v>320</v>
@@ -1002,12 +1099,18 @@
         <v>320</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>4000</v>
@@ -1028,7 +1131,11 @@
         <v>4000</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/CODERS scripts/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBF05A67-2B30-4929-8C0C-148082002F09}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA1DC616-41B6-4427-8CE5-7E878A34A2B5}"/>
   <bookViews>
-    <workbookView xWindow="-13035" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ON" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>tech</t>
   </si>
@@ -114,22 +114,58 @@
     <t>note</t>
   </si>
   <si>
-    <t>batches of new capacity</t>
-  </si>
-  <si>
-    <t>new biogas generation potential for ontario</t>
-  </si>
-  <si>
-    <t>new hydroelectric generation potential for ontario</t>
-  </si>
-  <si>
     <t>Sets the maximum capacity of technologies by period. One sheet per region.</t>
   </si>
   <si>
     <t>dq_est</t>
   </si>
   <si>
-    <t>asdas</t>
+    <t>Green, Jennifer, &amp; IESO. (2023). 2023 Annual Acquisition Report—Feedback from Canadian Biogas Association. IESO. https://www.ieso.ca/-/media/Files/IESO/Document-Library/engage/aar/2023-aar-20230309-canadian-biogas-association.ashx</t>
+  </si>
+  <si>
+    <t>New hydro development opportunities. (2023, February 9). OPG. https://www.opg.com/projects-services/projects/hydroelectric-development/new-hydro/</t>
+  </si>
+  <si>
+    <t>Batches of new onshore wind capacity</t>
+  </si>
+  <si>
+    <t>Batches of new solar PV capacity</t>
+  </si>
+  <si>
+    <t>New biogas generation potential for ontario</t>
+  </si>
+  <si>
+    <t>New hydroelectric generation potential for ontario. Half assumed to be run-of-river, the other half daily storage.</t>
+  </si>
+  <si>
+    <t>Assumed that Ontario does not have requisite geology for geothermal generation</t>
+  </si>
+  <si>
+    <t>Ontario does not have suitable sites</t>
+  </si>
+  <si>
+    <t>E_GEO-NEW</t>
+  </si>
+  <si>
+    <t>E_HYD_MLY-NEW</t>
+  </si>
+  <si>
+    <t>E_HYD_ANN-NEW</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-1</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-2</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-3</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-4</t>
+  </si>
+  <si>
+    <t>E_HYD_ROR-NEW-5</t>
   </si>
 </sst>
 </file>
@@ -488,15 +524,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D36A0F-FD90-42AA-87C7-33795DBA1E16}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -530,10 +567,10 @@
         <v>25</v>
       </c>
       <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
         <v>24</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -559,9 +596,9 @@
         <v>1000</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -586,9 +623,9 @@
         <v>1000</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -613,9 +650,9 @@
         <v>1000</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -640,9 +677,9 @@
         <v>1000</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -667,9 +704,9 @@
         <v>1000</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -694,9 +731,9 @@
         <v>1000</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -721,9 +758,9 @@
         <v>1000</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -748,9 +785,9 @@
         <v>1000</v>
       </c>
       <c r="H11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -775,9 +812,9 @@
         <v>1000</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -802,9 +839,9 @@
         <v>1000</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -829,9 +866,9 @@
         <v>2000</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -856,9 +893,9 @@
         <v>2000</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -883,9 +920,9 @@
         <v>2000</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -910,9 +947,9 @@
         <v>2000</v>
       </c>
       <c r="H17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -937,9 +974,9 @@
         <v>2000</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -964,9 +1001,9 @@
         <v>2000</v>
       </c>
       <c r="H19" t="s">
-        <v>26</v>
-      </c>
-      <c r="I19" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -991,9 +1028,9 @@
         <v>2000</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -1018,9 +1055,9 @@
         <v>2000</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -1045,9 +1082,9 @@
         <v>2000</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1072,40 +1109,40 @@
         <v>2000</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C24">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D24">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E24">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F24">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G24">
         <v>320</v>
       </c>
       <c r="H24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24">
+        <v>32</v>
+      </c>
+      <c r="I24">
         <v>1</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1113,29 +1150,281 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="C25">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="D25">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="E25">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="F25">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="G25">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="H25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="1"/>
-      <c r="J25">
+        <v>33</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27">
         <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29">
+        <v>500</v>
+      </c>
+      <c r="C29">
+        <v>500</v>
+      </c>
+      <c r="D29">
+        <v>500</v>
+      </c>
+      <c r="E29">
+        <v>500</v>
+      </c>
+      <c r="F29">
+        <v>500</v>
+      </c>
+      <c r="G29">
+        <v>500</v>
+      </c>
+      <c r="H29" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30">
+        <v>500</v>
+      </c>
+      <c r="C30">
+        <v>500</v>
+      </c>
+      <c r="D30">
+        <v>500</v>
+      </c>
+      <c r="E30">
+        <v>500</v>
+      </c>
+      <c r="F30">
+        <v>500</v>
+      </c>
+      <c r="G30">
+        <v>500</v>
+      </c>
+      <c r="H30" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31">
+        <v>500</v>
+      </c>
+      <c r="C31">
+        <v>500</v>
+      </c>
+      <c r="D31">
+        <v>500</v>
+      </c>
+      <c r="E31">
+        <v>500</v>
+      </c>
+      <c r="F31">
+        <v>500</v>
+      </c>
+      <c r="G31">
+        <v>500</v>
+      </c>
+      <c r="H31" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32">
+        <v>500</v>
+      </c>
+      <c r="C32">
+        <v>500</v>
+      </c>
+      <c r="D32">
+        <v>500</v>
+      </c>
+      <c r="E32">
+        <v>500</v>
+      </c>
+      <c r="F32">
+        <v>500</v>
+      </c>
+      <c r="G32">
+        <v>500</v>
+      </c>
+      <c r="H32" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33">
+        <v>500</v>
+      </c>
+      <c r="C33">
+        <v>500</v>
+      </c>
+      <c r="D33">
+        <v>500</v>
+      </c>
+      <c r="E33">
+        <v>500</v>
+      </c>
+      <c r="F33">
+        <v>500</v>
+      </c>
+      <c r="G33">
+        <v>500</v>
+      </c>
+      <c r="H33" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="149" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A7C86A0-032B-4379-B4FC-965CC902B741}"/>
   <bookViews>
-    <workbookView xWindow="-26895" yWindow="4515" windowWidth="21600" windowHeight="11385" firstSheet="5" activeTab="9" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="-28920" yWindow="2490" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="6" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
     <sheet name="AB" sheetId="2" r:id="rId1"/>
